--- a/artfynd/A 8659-2024 artfynd.xlsx
+++ b/artfynd/A 8659-2024 artfynd.xlsx
@@ -6358,11 +6358,11 @@
         <v>120724120</v>
       </c>
       <c r="B52" t="n">
-        <v>91122</v>
+        <v>91168</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10049,11 +10049,11 @@
         <v>120723860</v>
       </c>
       <c r="B88" t="n">
-        <v>91122</v>
+        <v>91168</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">

--- a/artfynd/A 8659-2024 artfynd.xlsx
+++ b/artfynd/A 8659-2024 artfynd.xlsx
@@ -6358,7 +6358,7 @@
         <v>120724120</v>
       </c>
       <c r="B52" t="n">
-        <v>91168</v>
+        <v>91182</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>120723860</v>
       </c>
       <c r="B88" t="n">
-        <v>91168</v>
+        <v>91182</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>

--- a/artfynd/A 8659-2024 artfynd.xlsx
+++ b/artfynd/A 8659-2024 artfynd.xlsx
@@ -6358,7 +6358,7 @@
         <v>120724120</v>
       </c>
       <c r="B52" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>120723860</v>
       </c>
       <c r="B88" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>

--- a/artfynd/A 8659-2024 artfynd.xlsx
+++ b/artfynd/A 8659-2024 artfynd.xlsx
@@ -6358,7 +6358,7 @@
         <v>120724120</v>
       </c>
       <c r="B52" t="n">
-        <v>91184</v>
+        <v>91185</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>120723860</v>
       </c>
       <c r="B88" t="n">
-        <v>91184</v>
+        <v>91185</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>

--- a/artfynd/A 8659-2024 artfynd.xlsx
+++ b/artfynd/A 8659-2024 artfynd.xlsx
@@ -6358,7 +6358,7 @@
         <v>120724120</v>
       </c>
       <c r="B52" t="n">
-        <v>91185</v>
+        <v>91194</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>120723860</v>
       </c>
       <c r="B88" t="n">
-        <v>91185</v>
+        <v>91194</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
